--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="392">
   <si>
     <t>Notes</t>
   </si>
@@ -1054,6 +1054,192 @@
   </si>
   <si>
     <t>Fri Jul 24 21:04:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 19:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:05:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:14:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:19:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:24:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:29:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:32:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:33:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:34:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:36:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:40:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:46:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:48:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:54:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:11:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:16:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:21:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:22:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:24:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:26:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:33:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:46:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 21:57:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:10:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:14:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:47:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:50:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:55:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:00:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:06:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:08:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:11:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:17:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:22:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:24:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:32:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:33:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:47:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:53:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 23:55:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:00:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:02:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:03:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:05:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:14:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:29:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:33:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:37:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:41:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:52:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 00:57:44 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1697,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>287</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -1549,7 +1735,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>288</v>
+        <v>366</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>181</v>
@@ -1587,7 +1773,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>289</v>
+        <v>367</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>181</v>
@@ -1625,7 +1811,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>290</v>
+        <v>368</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -1666,7 +1852,7 @@
         <v>136</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>184</v>
@@ -1707,7 +1893,7 @@
         <v>136</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>292</v>
+        <v>370</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>184</v>
@@ -2951,7 +3137,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -3049,7 +3235,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>285</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -3150,7 +3336,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3249,7 +3435,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3348,7 +3534,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>309</v>
+        <v>387</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3541,7 +3727,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>313</v>
+        <v>388</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3640,7 +3826,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>317</v>
+        <v>389</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3736,7 +3922,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3830,7 +4016,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>294</v>
+        <v>373</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3924,7 +4110,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4015,10 +4201,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>297</v>
+        <v>375</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4112,7 +4298,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>323</v>
+        <v>385</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4209,7 +4395,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>286</v>
+        <v>364</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4475,7 +4661,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>319</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -4569,7 +4755,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>293</v>
+        <v>371</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4663,7 +4849,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>298</v>
+        <v>377</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4757,7 +4943,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>299</v>
+        <v>380</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="488">
   <si>
     <t>Notes</t>
   </si>
@@ -1240,6 +1240,294 @@
   </si>
   <si>
     <t>Thu Aug 20 00:57:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 22:28:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 22:58:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 23:19:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 23:34:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 23:47:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:04:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:05:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:08:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:09:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:11:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:27:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 00:44:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:06:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:26:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:35:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:42:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:56:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:58:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 01:59:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 02:01:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 02:19:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 02:37:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 02:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 02:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 03:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 03:41:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 03 03:53:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:00:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:06:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:10:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:15:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:20:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:21:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:22:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:23:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:24:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:25:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:30:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:35:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:36:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:53:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:58:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:04:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:07:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:09:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:10:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:12:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:27:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:38:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:46:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 03:52:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 04:07:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:11:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:44:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:47:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:52:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:44:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 07:52:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:06:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:11:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:17:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:19:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:20:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:21:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:22:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:24:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:29:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:53:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:02:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:04:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:10:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:11:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:36:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:45:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:46:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 09:51:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:02:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 10:07:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 19:50:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 19:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 20:01:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1697,7 +1985,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>365</v>
+        <v>460</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -1735,7 +2023,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>366</v>
+        <v>461</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>181</v>
@@ -1773,7 +2061,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>367</v>
+        <v>462</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>181</v>
@@ -1811,7 +2099,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>368</v>
+        <v>463</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>184</v>
@@ -1852,7 +2140,7 @@
         <v>136</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>184</v>
@@ -1893,7 +2181,7 @@
         <v>136</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>370</v>
+        <v>465</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>184</v>
@@ -3137,7 +3425,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>362</v>
+        <v>457</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -3235,7 +3523,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>363</v>
+        <v>458</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
@@ -3336,7 +3624,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>361</v>
+        <v>456</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3435,7 +3723,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>386</v>
+        <v>478</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3534,7 +3822,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>387</v>
+        <v>479</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3727,7 +4015,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>388</v>
+        <v>481</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3826,7 +4114,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>389</v>
+        <v>482</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3922,7 +4210,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>378</v>
+        <v>470</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4016,7 +4304,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>373</v>
+        <v>467</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4107,10 +4395,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>384</v>
+        <v>476</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4201,10 +4489,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>375</v>
+        <v>487</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4298,7 +4586,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>385</v>
+        <v>477</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4395,7 +4683,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>364</v>
+        <v>459</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4661,7 +4949,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>391</v>
+        <v>484</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>181</v>
@@ -4755,7 +5043,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>371</v>
+        <v>466</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4849,7 +5137,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>377</v>
+        <v>469</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4943,7 +5231,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>380</v>
+        <v>472</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="492">
   <si>
     <t>Notes</t>
   </si>
@@ -1528,6 +1528,18 @@
   </si>
   <si>
     <t>Wed Oct 21 20:01:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:40:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:43:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 03:45:33 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3520,10 +3532,10 @@
     </row>
     <row ht="100.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>184</v>
